--- a/04-实施战略/03-实施工具/01-Kaizen事件策划模板.xlsx
+++ b/04-实施战略/03-实施工具/01-Kaizen事件策划模板.xlsx
@@ -96,7 +96,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -123,11 +123,20 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="001F3A5F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -151,6 +160,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -534,7 +544,13 @@
           <t>01-Kaizen事件策划模板</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+      <c r="D1" s="11" t="n"/>
+      <c r="E1" s="11" t="n"/>
+      <c r="F1" s="11" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -542,6 +558,10 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -549,6 +569,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
@@ -556,6 +577,9 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
@@ -563,6 +587,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
@@ -570,6 +595,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
@@ -577,6 +603,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
@@ -605,6 +632,9 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -612,6 +642,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
@@ -619,6 +650,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
@@ -626,6 +658,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
@@ -661,6 +694,9 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
@@ -668,6 +704,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
@@ -675,6 +712,7 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
@@ -682,6 +720,7 @@
         </is>
       </c>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
@@ -689,6 +728,7 @@
         </is>
       </c>
     </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
@@ -696,6 +736,7 @@
         </is>
       </c>
     </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
@@ -703,6 +744,7 @@
         </is>
       </c>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
@@ -710,6 +752,7 @@
         </is>
       </c>
     </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
@@ -717,6 +760,7 @@
         </is>
       </c>
     </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
@@ -724,6 +768,7 @@
         </is>
       </c>
     </row>
+    <row r="58"/>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
@@ -731,6 +776,7 @@
         </is>
       </c>
     </row>
+    <row r="60"/>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
@@ -738,6 +784,9 @@
         </is>
       </c>
     </row>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
@@ -745,6 +794,7 @@
         </is>
       </c>
     </row>
+    <row r="66"/>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
@@ -752,6 +802,9 @@
         </is>
       </c>
     </row>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
@@ -759,6 +812,7 @@
         </is>
       </c>
     </row>
+    <row r="72"/>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
@@ -766,6 +820,9 @@
         </is>
       </c>
     </row>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
@@ -773,6 +830,7 @@
         </is>
       </c>
     </row>
+    <row r="78"/>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
@@ -808,6 +866,7 @@
         </is>
       </c>
     </row>
+    <row r="84"/>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
@@ -815,6 +874,7 @@
         </is>
       </c>
     </row>
+    <row r="86"/>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
@@ -1163,7 +1223,7 @@
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>□ 冷镦 □ 搓丝 □ 热处理 □ 表面处理 □ 包装 □ 其他：_____</t>
+          <t>□ 机加工 □ 精加工 □ 热处理 □ 表面处理 □ 包装 □ 其他：_____</t>
         </is>
       </c>
     </row>
